--- a/Docs/weekly sprint/Sprint_17.xlsx
+++ b/Docs/weekly sprint/Sprint_17.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0d25a1f11c8555b/Desktop/SpaceLandMapper Docs/weekly sprint/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_4A43F297174C90BFEF1744F55597EE3F0792CE34" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_4A43F297174C90BFEF1744F55597EE3F0792CE34" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A91E931-5F2F-43B0-A1C1-CE0D02916684}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
